--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_548_Vanuatu.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_548_Vanuatu.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rcb3637280de24761"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rbbf0212787784fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re84d5d0c2b744a98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rbb1bc720afac4780"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8556d22f8eab48f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R21b0e3c8f3524c24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Red63bdc82076463e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R3a525c16bc994a32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R7b4b8f648f464166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3d7f707e77bf42c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R69801c13661e48d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R550eb9ffbeda4aaa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ548CommercialTable" displayName="EEZ548CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ548CommercialTable" displayName="EEZ548CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ548FunctionalTable" displayName="EEZ548FunctionalTable" ref="A1:O15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O15"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ548FunctionalTable" displayName="EEZ548FunctionalTable" ref="A1:E15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E15"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ548ValidationTable" displayName="EEZ548ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ548ValidationTable" displayName="EEZ548ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5250,7 +5204,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb83e2537f8ce415e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57eac6a59ff54b72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5260,20 +5214,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5281,444 +5225,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1302.0279166002001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.112999999991689</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>129.71792709591318</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1302.0279166002001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>131.64768622530158</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$69,A2,'Species'!$U$2:$U$69))</x:f>
-        <x:v>171408.96262116628</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.112999999991689</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>129.71792709591318</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>168896.3623623885</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2512.600258777791</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0148765800733275</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.014876580073327391</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>25.61972404</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>25.61972404</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$69,A3,'Species'!$U$2:$U$69))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3703.176804295154</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>3703.176804295154</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>525.588644364</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.7385151129332628</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>54.766515872875246</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>525.588644364</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>85.05895627346192</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$69,A4,'Species'!$U$2:$U$69))</x:f>
-        <x:v>44706.021518785594</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.7385151129332628</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>54.766515872875246</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>28784.658834163987</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>15921.362684621607</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.5531197286842542</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.5531197286842543</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2610.178643897201</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2618483565522483</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>182.74620062686316</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2610.178643897201</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>191.6086722100565</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$69,A5,'Species'!$U$2:$U$69))</x:f>
-        <x:v>500132.86418818857</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2618483565522483</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>182.74620062686316</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>477000.2301295915</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>23132.63405859709</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0484960647761374</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04849606477613735</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2188.6375088519994</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.4060231137115387</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>254.69658017774847</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2188.6375088519994</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>795.7766568056651</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$69,A6,'Species'!$U$2:$U$69))</x:f>
-        <x:v>1741666.6397537233</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.4060231137115387</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>254.69658017774847</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>557438.4887533509</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1184228.1510003724</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>3.124410450467399</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>2.124410450467399</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3456.6962850120003</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.3678544193289</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2332.6759904970045</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3456.6962850120003</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2362.3532380359748</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$69,A7,'Species'!$U$2:$U$69))</x:f>
-        <x:v>8165937.661805023</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.3678544193289</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2332.6759904970045</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>8063352.430487684</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>102585.23131733947</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0127224045087577</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.012722404508757773</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>9522.1125718242</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.358126510030556</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2281.006432657375</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>9522.1125718242</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2313.7155451941812</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$69,A8,'Species'!$U$2:$U$69))</x:f>
-        <x:v>22031459.880518597</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.358126510030556</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2281.006432657375</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>21720000.028818663</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>311459.8516999334</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0143397721586869</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.014339772158686941</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a80fa1db28b401f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R954ccb57c36b47d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5728,20 +5383,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5749,822 +5394,288 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>12.2790191851</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.42</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2630.2679918953813</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>12.2790191851</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$69,A2,'Species'!$U$2:$U$69))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>32297.111134437837</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.42</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>32297.111134437837</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>25.61972404</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.03</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>10.71519305237606</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>25.61972404</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>10.715193052376058</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$69,A3,'Species'!$U$2:$U$69))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>274.5202890371999</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.03</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>10.71519305237606</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>274.5202890371999</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>21.6212711501</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.49</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>3090.295432513592</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>21.6212711501</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>3090.2954325135925</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$69,A4,'Species'!$U$2:$U$69))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>66816.11548029193</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.49</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>66816.11548029193</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>9610.6235683887</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.358214528369989</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2281.468770433284</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>9610.6235683887</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2313.894838394538</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$69,A5,'Species'!$U$2:$U$69))</x:f>
-        <x:v>22237972.26864751</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.358214528369989</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2281.468770433284</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>21926337.53566891</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>311634.732978601</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.014212803778636</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.01421280377863589</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3456.6962850120003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.3678544193289</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2332.6759904970045</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3456.6962850120003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2362.3532380359748</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$69,A6,'Species'!$U$2:$U$69))</x:f>
-        <x:v>8165937.661805023</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.3678544193289</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2332.6759904970045</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>8063352.430487684</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>102585.23131733947</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0127224045087577</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.012722404508757773</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1302.0279166002001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.112999999991689</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>129.71792709591318</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1302.0279166002001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>131.64768622530158</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$69,A7,'Species'!$U$2:$U$69))</x:f>
-        <x:v>171408.96262116628</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.112999999991689</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>129.71792709591318</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>168896.3623623885</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2512.600258777791</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0148765800733275</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.014876580073327391</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.5383058732</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.5383058732</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$69,A8,'Species'!$U$2:$U$69))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1233.1875122087915</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>1233.1875122087915</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2060.6067105775996</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.2910770466405364</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>195.46861989487792</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2060.6067105775996</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>199.37658857737833</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$69,A9,'Species'!$U$2:$U$69))</x:f>
-        <x:v>410836.73635461496</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.2910770466405364</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>195.46861989487792</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>402783.94986272755</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>8052.786491887411</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0199928187174088</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.01999281871740886</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>783.7596140684</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6821361507615578</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>480.99011459835225</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>783.7596140684</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>875.5682832312847</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$69,A10,'Species'!$U$2:$U$69))</x:f>
-        <x:v>686235.0597558832</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6821361507615578</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>480.99011459835225</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>376980.62658832</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>309254.43316756317</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.8203456924731654</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.8203456924731654</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1498.4438228502997</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.209310331110388</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>161.92366722405228</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1498.4438228502997</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>526.1257350018612</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$69,A11,'Species'!$U$2:$U$69))</x:f>
-        <x:v>788369.8576561126</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.209310331110388</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>161.92366722405228</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>242633.51892514867</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>545736.338730964</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>3.249220722464653</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>2.249220722464653</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>525.588644364</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.7385151129332628</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>54.766515872875246</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>525.588644364</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>85.05895627346192</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$69,A12,'Species'!$U$2:$U$69))</x:f>
-        <x:v>44706.021518785594</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.7385151129332628</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>54.766515872875246</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>28784.658834163987</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>15921.362684621607</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.5531197286842542</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.5531197286842543</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>25.61972404</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.0299999999999994</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>107.15193052376048</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>25.61972404</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$69,A13,'Species'!$U$2:$U$69))</x:f>
-        <x:v>2745.2028903719993</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.0299999999999994</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>107.15193052376048</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>2745.2028903719965</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>2.7284841053187847e-12</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>9.93909818064141e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>25.61972404</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>25.61972404</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$69,A14,'Species'!$U$2:$U$69))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>3703.176804295154</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>3703.176804295154</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>281.81696439999996</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.917272727277308</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>82.65568459516973</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>281.81696439999996</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>164.9273486392071</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$69,A15,'Species'!$U$2:$U$69))</x:f>
-        <x:v>46479.32474004181</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.917272727277308</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>82.65568459516973</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>23293.774123014573</x:v>
       </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>23185.55061702724</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.9953539728935377</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.9953539728935378</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G15">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O15">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8f7d2ffb61d4244"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4b9016381e042df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6739,7 +5850,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6838,7 +5949,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>32659015.20720978</x:v>
+        <x:v>31019175.376190137</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6852,7 +5963,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>32659015.207209785</x:v>
+        <x:v>31340132.170963</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6866,7 +5977,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1639839.8310196437</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6880,7 +5991,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-1318883.0362467803</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6891,9 +6002,9 @@
         <x:v>EEZ_548</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6905,47 +6016,19 @@
         <x:v>EEZ_548</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_548</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_548</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8346124953c7443b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9acd7e475bc7477d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6992,7 +6075,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
